--- a/saida/isaias01_taxa_servico_prova_fechada_set_out_2026.xlsx
+++ b/saida/isaias01_taxa_servico_prova_fechada_set_out_2026.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -450,10 +450,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C2" t="n">
-        <v>2070.5</v>
+        <v>2122.2</v>
       </c>
     </row>
     <row r="3">
@@ -463,10 +463,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" t="n">
-        <v>1531.95</v>
+        <v>1554.2</v>
       </c>
     </row>
     <row r="4">
@@ -476,10 +476,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C4" t="n">
-        <v>3602.45</v>
+        <v>3676.4</v>
       </c>
     </row>
     <row r="5"/>
@@ -487,54 +487,99 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Critério</t>
+          <t>Operador do caixa</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cupons</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cobrado a mais (R$)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cupom fechado no PDV sem o item TAXA DE SERVICO (coluna "Item taxa no cupom" = não).</t>
-        </is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>219</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3602.45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Na maquininha Sicredi, no mesmo caixa e poucos minutos antes do fechamento, uma venda aprovada de valor exatamente igual ao cupom × 1,10 (±1 centavo).</t>
-        </is>
+          <t>LUCAS DE MUSSI PALMA</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>73.95</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Terminal da venda é de uso exclusivo do caixa do cupom (≥ 95% dos casamentos exatos do período no mesmo caixa), ou seja, a venda não pode ser de outro PDV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Nenhum outro cupom livre com o valor da máquina no turno e nenhuma outra venda livre da máquina com o valor do cupom: o par é único.</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Operador do caixa é o que consta no relatório de cupons do PDV para aquele cupom; atendente e mesa vêm do relatório analítico.</t>
+          <t>Critério</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fora desta lista: cupons com qualquer ponto em aberto na prova ("ver observação") e cupons de outros operadores.</t>
+          <t>Cupom fechado no PDV sem o item TAXA DE SERVICO (coluna "Item taxa no cupom" = não).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
+        <is>
+          <t>Na maquininha Sicredi, no mesmo caixa e poucos minutos antes do fechamento, uma venda aprovada de valor exatamente igual ao cupom × 1,10 (±1 centavo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Terminal da venda é de uso exclusivo do caixa do cupom (≥ 95% dos casamentos exatos do período no mesmo caixa), ou seja, a venda não pode ser de outro PDV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Nenhum outro cupom livre com o valor da máquina no turno e nenhuma outra venda livre da máquina com o valor do cupom: o par é único.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Operador do caixa é o login registrado no relatório de cupons do PDV para aquele cupom; atendente e mesa vêm do relatório analítico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fora desta lista: cupons com qualquer ponto em aberto na prova ("ver observação").</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>O valor cobrado a mais entrou na conta da empresa pela Sicredi (PIX, crédito ou débito); a lista mede a diferença entre o que a máquina cobrou e o que o PDV registrou.</t>
         </is>
@@ -551,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W220"/>
+  <dimension ref="A1:W225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10994,21 +11039,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>dom</t>
+          <t>sáb</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>23:17</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>41866</v>
+        <v>41846</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11017,38 +11062,38 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>BRUNO DA SILVA INACIO</t>
+          <t>LUCAS DE MUSSI PALMA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6</v>
+        <v>264</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>210</v>
+        <v>128</v>
       </c>
       <c r="L100" t="n">
-        <v>231</v>
+        <v>140.8</v>
       </c>
       <c r="M100" t="n">
-        <v>21</v>
+        <v>12.8</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>23:17</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -11067,7 +11112,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>720952</t>
+          <t>SE001000000000EUNB4DN4S7HADECGGT25</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
@@ -11099,21 +11144,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>dom</t>
+          <t>sáb</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>41873</v>
+        <v>41848</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11122,38 +11167,38 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>BRUNO DA SILVA INACIO</t>
+          <t>LUCAS DE MUSSI PALMA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="L101" t="n">
-        <v>214.5</v>
+        <v>228.8</v>
       </c>
       <c r="M101" t="n">
-        <v>19.5</v>
+        <v>20.8</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -11172,7 +11217,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>6O87GD</t>
+          <t>473672</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
@@ -11214,11 +11259,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>41881</v>
+        <v>41866</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11232,33 +11277,33 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I102" t="n">
+        <v>6</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Crédito</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>210</v>
+      </c>
+      <c r="L102" t="n">
+        <v>231</v>
+      </c>
+      <c r="M102" t="n">
         <v>21</v>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Crédito</t>
-        </is>
-      </c>
-      <c r="K102" t="n">
-        <v>188.5</v>
-      </c>
-      <c r="L102" t="n">
-        <v>207.35</v>
-      </c>
-      <c r="M102" t="n">
-        <v>18.85</v>
-      </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>21:27</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="O102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
@@ -11277,7 +11322,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>672095</t>
+          <t>720952</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -11319,11 +11364,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>41882</v>
+        <v>41873</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11341,7 +11386,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -11349,17 +11394,17 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="L103" t="n">
-        <v>226.6</v>
+        <v>214.5</v>
       </c>
       <c r="M103" t="n">
-        <v>20.6</v>
+        <v>19.5</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="O103" t="n">
@@ -11382,7 +11427,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>453527</t>
+          <t>6O87GD</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -11414,21 +11459,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>dom</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>41992</v>
+        <v>41881</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11442,11 +11487,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -11454,17 +11499,17 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>130</v>
+        <v>188.5</v>
       </c>
       <c r="L104" t="n">
-        <v>143</v>
+        <v>207.35</v>
       </c>
       <c r="M104" t="n">
-        <v>13</v>
+        <v>18.85</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="O104" t="n">
@@ -11487,7 +11532,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>945743</t>
+          <t>672095</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -11519,21 +11564,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>qua</t>
+          <t>dom</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>42069</v>
+        <v>41882</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11547,33 +11592,33 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>BRUNO DA SILVA INACIO</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K105" t="n">
-        <v>293.1</v>
+        <v>206</v>
       </c>
       <c r="L105" t="n">
-        <v>322.41</v>
+        <v>226.6</v>
       </c>
       <c r="M105" t="n">
-        <v>29.31</v>
+        <v>20.6</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="O105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
@@ -11592,7 +11637,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>S32856</t>
+          <t>453527</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -11624,21 +11669,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>qua</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>42081</v>
+        <v>41992</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11652,33 +11697,33 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K106" t="n">
-        <v>205.5</v>
+        <v>130</v>
       </c>
       <c r="L106" t="n">
-        <v>226.05</v>
+        <v>143</v>
       </c>
       <c r="M106" t="n">
-        <v>20.55</v>
+        <v>13</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
@@ -11697,7 +11742,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>264250</t>
+          <t>945743</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
@@ -11739,11 +11784,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>42089</v>
+        <v>42069</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11757,33 +11802,33 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t>BRUNO DA SILVA INACIO</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>263</v>
+        <v>27</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K107" t="n">
-        <v>100.5</v>
+        <v>293.1</v>
       </c>
       <c r="L107" t="n">
-        <v>110.55</v>
+        <v>322.41</v>
       </c>
       <c r="M107" t="n">
-        <v>10.05</v>
+        <v>29.31</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -11802,7 +11847,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>409037</t>
+          <t>S32856</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
@@ -11834,21 +11879,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>qua</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>42150</v>
+        <v>42081</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11862,42 +11907,42 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K108" t="n">
-        <v>186</v>
+        <v>205.5</v>
       </c>
       <c r="L108" t="n">
-        <v>204.6</v>
+        <v>226.05</v>
       </c>
       <c r="M108" t="n">
-        <v>18.6</v>
+        <v>20.55</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>PDV 02 em 113 de 113 casamentos exatos</t>
+          <t>PDV 02 em 95 de 95 casamentos exatos</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -11907,7 +11952,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>SE00100000000054V46LM7DQTM2OLMV222</t>
+          <t>264250</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
@@ -11939,21 +11984,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>qua</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>42158</v>
+        <v>42089</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11967,11 +12012,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>263</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -11979,30 +12024,30 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>156.5</v>
+        <v>100.5</v>
       </c>
       <c r="L109" t="n">
-        <v>172.15</v>
+        <v>110.55</v>
       </c>
       <c r="M109" t="n">
-        <v>15.65</v>
+        <v>10.05</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>PDV 02 em 113 de 113 casamentos exatos</t>
+          <t>PDV 02 em 95 de 95 casamentos exatos</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -12012,7 +12057,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>176679</t>
+          <t>409037</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
@@ -12054,11 +12099,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>42165</v>
+        <v>42150</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12072,33 +12117,33 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K110" t="n">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="L110" t="n">
-        <v>228.8</v>
+        <v>204.6</v>
       </c>
       <c r="M110" t="n">
-        <v>20.8</v>
+        <v>18.6</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
@@ -12117,7 +12162,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>R95626</t>
+          <t>SE00100000000054V46LM7DQTM2OLMV222</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
@@ -12159,11 +12204,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>22:07</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>42174</v>
+        <v>42158</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12177,33 +12222,33 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K111" t="n">
-        <v>181</v>
+        <v>156.5</v>
       </c>
       <c r="L111" t="n">
-        <v>199.1</v>
+        <v>172.15</v>
       </c>
       <c r="M111" t="n">
-        <v>18.1</v>
+        <v>15.65</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
@@ -12222,7 +12267,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>SE001000000000JTKBCU8DH7OYYCT79C3E</t>
+          <t>176679</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
@@ -12264,11 +12309,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>42187</v>
+        <v>42165</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12282,33 +12327,33 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>229</v>
+        <v>11</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K112" t="n">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="L112" t="n">
-        <v>46.2</v>
+        <v>228.8</v>
       </c>
       <c r="M112" t="n">
-        <v>4.2</v>
+        <v>20.8</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>22:21</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -12327,7 +12372,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>SE0010000000008OIVJYIW1HQDBIHFS6A4</t>
+          <t>R95626</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
@@ -12369,11 +12414,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>22:23</t>
+          <t>22:07</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>42188</v>
+        <v>42174</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12387,11 +12432,11 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>195</v>
+        <v>6</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -12399,21 +12444,21 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>215.5</v>
+        <v>181</v>
       </c>
       <c r="L113" t="n">
-        <v>237.05</v>
+        <v>199.1</v>
       </c>
       <c r="M113" t="n">
-        <v>21.55</v>
+        <v>18.1</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>22:23</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
@@ -12432,7 +12477,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>SE0010000000002RLFTK2BQUDX38QH7ZD4</t>
+          <t>SE001000000000JTKBCU8DH7OYYCT79C3E</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
@@ -12474,11 +12519,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>22:42</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>42200</v>
+        <v>42187</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12492,33 +12537,33 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>18</v>
+        <v>229</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K114" t="n">
-        <v>148.5</v>
+        <v>42</v>
       </c>
       <c r="L114" t="n">
-        <v>163.35</v>
+        <v>46.2</v>
       </c>
       <c r="M114" t="n">
-        <v>14.85</v>
+        <v>4.2</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:21</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
@@ -12537,7 +12582,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>672622</t>
+          <t>SE0010000000008OIVJYIW1HQDBIHFS6A4</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
@@ -12569,21 +12614,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>42224</v>
+        <v>42188</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12601,7 +12646,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>47</v>
+        <v>195</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -12609,30 +12654,30 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>176</v>
+        <v>215.5</v>
       </c>
       <c r="L115" t="n">
-        <v>193.6</v>
+        <v>237.05</v>
       </c>
       <c r="M115" t="n">
-        <v>17.6</v>
+        <v>21.55</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="O115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>PDV 02 em 95 de 95 casamentos exatos</t>
+          <t>PDV 02 em 113 de 113 casamentos exatos</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -12642,7 +12687,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>SE001000000000LFNPDU7RCJ4LMQCCVOL6</t>
+          <t>SE0010000000002RLFTK2BQUDX38QH7ZD4</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -12674,21 +12719,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>22:42</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>42229</v>
+        <v>42200</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12702,42 +12747,42 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K116" t="n">
-        <v>162</v>
+        <v>148.5</v>
       </c>
       <c r="L116" t="n">
-        <v>178.2</v>
+        <v>163.35</v>
       </c>
       <c r="M116" t="n">
-        <v>16.2</v>
+        <v>14.85</v>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="O116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>PDV 02 em 95 de 95 casamentos exatos</t>
+          <t>PDV 02 em 113 de 113 casamentos exatos</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -12747,7 +12792,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>R09077</t>
+          <t>672622</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -12789,11 +12834,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>42233</v>
+        <v>42224</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12807,33 +12852,33 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K117" t="n">
-        <v>203.5</v>
+        <v>176</v>
       </c>
       <c r="L117" t="n">
-        <v>223.85</v>
+        <v>193.6</v>
       </c>
       <c r="M117" t="n">
-        <v>20.35</v>
+        <v>17.6</v>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -12852,7 +12897,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>150270</t>
+          <t>SE001000000000LFNPDU7RCJ4LMQCCVOL6</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -12894,11 +12939,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>42237</v>
+        <v>42229</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12912,42 +12957,42 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K118" t="n">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="L118" t="n">
-        <v>238.7</v>
+        <v>178.2</v>
       </c>
       <c r="M118" t="n">
-        <v>21.7</v>
+        <v>16.2</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>PDV 02 em 113 de 113 casamentos exatos</t>
+          <t>PDV 02 em 95 de 95 casamentos exatos</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -12957,7 +13002,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>177195</t>
+          <t>R09077</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
@@ -12999,11 +13044,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>42238</v>
+        <v>42233</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13021,7 +13066,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -13029,21 +13074,21 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>260</v>
+        <v>203.5</v>
       </c>
       <c r="L119" t="n">
-        <v>286</v>
+        <v>223.85</v>
       </c>
       <c r="M119" t="n">
-        <v>26</v>
+        <v>20.35</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>21:27</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="O119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
@@ -13062,7 +13107,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>176298</t>
+          <t>150270</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
@@ -13104,11 +13149,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>21:56</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>42249</v>
+        <v>42237</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13122,42 +13167,42 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K120" t="n">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="L120" t="n">
-        <v>216.7</v>
+        <v>238.7</v>
       </c>
       <c r="M120" t="n">
-        <v>19.7</v>
+        <v>21.7</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>PDV 02 em 95 de 95 casamentos exatos</t>
+          <t>PDV 02 em 113 de 113 casamentos exatos</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -13167,7 +13212,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>SE001000000000HV8GK08E558YS0NOELI3</t>
+          <t>177195</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -13209,11 +13254,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>21:56</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>42250</v>
+        <v>42238</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13227,11 +13272,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -13239,21 +13284,21 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L121" t="n">
-        <v>288.2</v>
+        <v>286</v>
       </c>
       <c r="M121" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="O121" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
@@ -13272,7 +13317,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>373486</t>
+          <t>176298</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
@@ -13314,11 +13359,11 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>22:07</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>42260</v>
+        <v>42249</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13332,33 +13377,33 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K122" t="n">
-        <v>155</v>
+        <v>197</v>
       </c>
       <c r="L122" t="n">
-        <v>170.5</v>
+        <v>216.7</v>
       </c>
       <c r="M122" t="n">
-        <v>15.5</v>
+        <v>19.7</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="O122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -13377,7 +13422,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>646652</t>
+          <t>SE001000000000HV8GK08E558YS0NOELI3</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
@@ -13419,11 +13464,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>22:42</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>42277</v>
+        <v>42250</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13437,33 +13482,33 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>180</v>
+        <v>35</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K123" t="n">
-        <v>103</v>
+        <v>262</v>
       </c>
       <c r="L123" t="n">
-        <v>113.3</v>
+        <v>288.2</v>
       </c>
       <c r="M123" t="n">
-        <v>10.3</v>
+        <v>26.2</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>22:42</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -13482,7 +13527,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>SE001000000000321NAFRVFVM27MK0JNCM</t>
+          <t>373486</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
@@ -13524,11 +13569,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>22:07</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>42286</v>
+        <v>42260</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13542,33 +13587,33 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>223</v>
+        <v>48</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K124" t="n">
-        <v>208.5</v>
+        <v>155</v>
       </c>
       <c r="L124" t="n">
-        <v>229.35</v>
+        <v>170.5</v>
       </c>
       <c r="M124" t="n">
-        <v>20.85</v>
+        <v>15.5</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -13587,7 +13632,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>SE001000000000LCPSEX7PPU89OC2EL2A4</t>
+          <t>646652</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
@@ -13619,21 +13664,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>dom</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>22:42</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>42492</v>
+        <v>42277</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13647,11 +13692,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -13659,30 +13704,30 @@
         </is>
       </c>
       <c r="K125" t="n">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="L125" t="n">
-        <v>157.3</v>
+        <v>113.3</v>
       </c>
       <c r="M125" t="n">
-        <v>14.3</v>
+        <v>10.3</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>22:42</t>
         </is>
       </c>
       <c r="O125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>PDV 02 em 113 de 113 casamentos exatos</t>
+          <t>PDV 02 em 95 de 95 casamentos exatos</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -13692,7 +13737,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>SE001000000000GPOBO4JN8JNQ39MEZEYS</t>
+          <t>SE001000000000321NAFRVFVM27MK0JNCM</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
@@ -13724,21 +13769,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>dom</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>42495</v>
+        <v>42286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13752,42 +13797,42 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>32</v>
+        <v>223</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K126" t="n">
-        <v>166</v>
+        <v>208.5</v>
       </c>
       <c r="L126" t="n">
-        <v>182.6</v>
+        <v>229.35</v>
       </c>
       <c r="M126" t="n">
-        <v>16.6</v>
+        <v>20.85</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="O126" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>PDV 02 em 113 de 113 casamentos exatos</t>
+          <t>PDV 02 em 95 de 95 casamentos exatos</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -13797,7 +13842,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>652801</t>
+          <t>SE001000000000LCPSEX7PPU89OC2EL2A4</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -13839,11 +13884,11 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>42500</v>
+        <v>42492</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13857,29 +13902,29 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K127" t="n">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="L127" t="n">
-        <v>187</v>
+        <v>157.3</v>
       </c>
       <c r="M127" t="n">
-        <v>17</v>
+        <v>14.3</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="O127" t="n">
@@ -13887,12 +13932,12 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>PDV 02 em 95 de 95 casamentos exatos</t>
+          <t>PDV 02 em 113 de 113 casamentos exatos</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -13902,7 +13947,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>092505</t>
+          <t>SE001000000000GPOBO4JN8JNQ39MEZEYS</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -13944,11 +13989,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>42502</v>
+        <v>42495</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13962,11 +14007,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -13974,30 +14019,30 @@
         </is>
       </c>
       <c r="K128" t="n">
-        <v>197.5</v>
+        <v>166</v>
       </c>
       <c r="L128" t="n">
-        <v>217.25</v>
+        <v>182.6</v>
       </c>
       <c r="M128" t="n">
-        <v>19.75</v>
+        <v>16.6</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="O128" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>PDV 02 em 95 de 95 casamentos exatos</t>
+          <t>PDV 02 em 113 de 113 casamentos exatos</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -14007,7 +14052,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>998166</t>
+          <t>652801</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
@@ -14049,11 +14094,11 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>22:18</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>42533</v>
+        <v>42500</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14071,38 +14116,38 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K129" t="n">
-        <v>157.5</v>
+        <v>170</v>
       </c>
       <c r="L129" t="n">
-        <v>173.25</v>
+        <v>187</v>
       </c>
       <c r="M129" t="n">
-        <v>15.75</v>
+        <v>17</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="O129" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>PDV 02 em 113 de 113 casamentos exatos</t>
+          <t>PDV 02 em 95 de 95 casamentos exatos</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -14112,7 +14157,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>5EHYKH</t>
+          <t>092505</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
@@ -14144,21 +14189,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>dom</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>42627</v>
+        <v>42502</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14176,38 +14221,38 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K130" t="n">
-        <v>178.5</v>
+        <v>197.5</v>
       </c>
       <c r="L130" t="n">
-        <v>196.35</v>
+        <v>217.25</v>
       </c>
       <c r="M130" t="n">
-        <v>17.85</v>
+        <v>19.75</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="O130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>PDV 02 em 113 de 113 casamentos exatos</t>
+          <t>PDV 02 em 95 de 95 casamentos exatos</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -14217,7 +14262,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>SE001000000000LGWHJYQK1BQ0PZ3EK5BE</t>
+          <t>998166</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -14249,21 +14294,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>qua</t>
+          <t>dom</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:18</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>42737</v>
+        <v>42533</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14277,33 +14322,33 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K131" t="n">
-        <v>94</v>
+        <v>157.5</v>
       </c>
       <c r="L131" t="n">
-        <v>103.4</v>
+        <v>173.25</v>
       </c>
       <c r="M131" t="n">
-        <v>9.4</v>
+        <v>15.75</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
@@ -14322,7 +14367,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>SE001000000000D7W236TV4R97M8YVFCO4</t>
+          <t>5EHYKH</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
@@ -14354,21 +14399,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>qua</t>
+          <t>dom</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>42742</v>
+        <v>42539</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14377,16 +14422,16 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>BRUNO DA SILVA INACIO</t>
+          <t>LUCAS DE MUSSI PALMA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -14394,21 +14439,21 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>52</v>
+        <v>181</v>
       </c>
       <c r="L132" t="n">
-        <v>57.2</v>
+        <v>199.1</v>
       </c>
       <c r="M132" t="n">
-        <v>5.2</v>
+        <v>18.1</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>23:09</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="O132" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
@@ -14427,7 +14472,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>SE001000000000AG6086F91OJH2A77XX72</t>
+          <t>SE0010000000006HBK86SW858PN0FLCYMW</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
@@ -14454,26 +14499,26 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>outubro/2026 (01 a 20)</t>
+          <t>setembro/2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>42804</v>
+        <v>42627</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14487,11 +14532,11 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>JOSE HENRIQUE ROSA</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -14499,21 +14544,21 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>269</v>
+        <v>178.5</v>
       </c>
       <c r="L133" t="n">
-        <v>295.9</v>
+        <v>196.35</v>
       </c>
       <c r="M133" t="n">
-        <v>26.9</v>
+        <v>17.85</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="O133" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -14522,7 +14567,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 113 de 113 casamentos exatos</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -14532,7 +14577,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>SE001000000000BRBCVVM85NVS4DB9SNO3</t>
+          <t>SE001000000000LGWHJYQK1BQ0PZ3EK5BE</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -14559,26 +14604,26 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>outubro/2026 (01 a 20)</t>
+          <t>setembro/2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>qua</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>42817</v>
+        <v>42737</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14596,29 +14641,29 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K134" t="n">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="L134" t="n">
-        <v>176</v>
+        <v>103.4</v>
       </c>
       <c r="M134" t="n">
-        <v>16</v>
+        <v>9.4</v>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="O134" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
@@ -14627,7 +14672,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 113 de 113 casamentos exatos</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -14637,7 +14682,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>375087</t>
+          <t>SE001000000000D7W236TV4R97M8YVFCO4</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -14664,26 +14709,26 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>outubro/2026 (01 a 20)</t>
+          <t>setembro/2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>qua</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>42818</v>
+        <v>42742</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14697,33 +14742,33 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>29</v>
+        <v>116</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K135" t="n">
-        <v>244</v>
+        <v>52</v>
       </c>
       <c r="L135" t="n">
-        <v>268.4</v>
+        <v>57.2</v>
       </c>
       <c r="M135" t="n">
-        <v>24.4</v>
+        <v>5.2</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>23:09</t>
         </is>
       </c>
       <c r="O135" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
@@ -14732,7 +14777,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 113 de 113 casamentos exatos</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -14742,7 +14787,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>645846</t>
+          <t>SE001000000000AG6086F91OJH2A77XX72</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
@@ -14784,11 +14829,11 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>42823</v>
+        <v>42804</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14802,33 +14847,33 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
+          <t>JOSE HENRIQUE ROSA</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K136" t="n">
-        <v>88</v>
+        <v>269</v>
       </c>
       <c r="L136" t="n">
-        <v>96.8</v>
+        <v>295.9</v>
       </c>
       <c r="M136" t="n">
-        <v>8.800000000000001</v>
+        <v>26.9</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="O136" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
@@ -14847,7 +14892,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>334980</t>
+          <t>SE001000000000BRBCVVM85NVS4DB9SNO3</t>
         </is>
       </c>
       <c r="T136" t="inlineStr">
@@ -14879,21 +14924,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>42877</v>
+        <v>42817</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14907,33 +14952,33 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K137" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="L137" t="n">
-        <v>166.1</v>
+        <v>176</v>
       </c>
       <c r="M137" t="n">
-        <v>15.1</v>
+        <v>16</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="O137" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
@@ -14952,7 +14997,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>302282</t>
+          <t>375087</t>
         </is>
       </c>
       <c r="T137" t="inlineStr">
@@ -14984,21 +15029,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>42878</v>
+        <v>42818</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15012,11 +15057,11 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -15024,21 +15069,21 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>88.5</v>
+        <v>244</v>
       </c>
       <c r="L138" t="n">
-        <v>97.34999999999999</v>
+        <v>268.4</v>
       </c>
       <c r="M138" t="n">
-        <v>8.85</v>
+        <v>24.4</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="O138" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
@@ -15057,7 +15102,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>096092</t>
+          <t>645846</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
@@ -15089,21 +15134,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>42879</v>
+        <v>42823</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15117,33 +15162,33 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>LUCAS DE MUSSI PALMA</t>
+          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K139" t="n">
-        <v>213.5</v>
+        <v>88</v>
       </c>
       <c r="L139" t="n">
-        <v>234.85</v>
+        <v>96.8</v>
       </c>
       <c r="M139" t="n">
-        <v>21.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
@@ -15162,7 +15207,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>NM7I3M</t>
+          <t>334980</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
@@ -15204,11 +15249,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>42880</v>
+        <v>42877</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15222,33 +15267,33 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K140" t="n">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="L140" t="n">
-        <v>187</v>
+        <v>166.1</v>
       </c>
       <c r="M140" t="n">
-        <v>17</v>
+        <v>15.1</v>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
@@ -15267,7 +15312,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>37820J</t>
+          <t>302282</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
@@ -15309,11 +15354,11 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>42884</v>
+        <v>42878</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15327,33 +15372,33 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K141" t="n">
-        <v>168.5</v>
+        <v>88.5</v>
       </c>
       <c r="L141" t="n">
-        <v>185.35</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="M141" t="n">
-        <v>16.85</v>
+        <v>8.85</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
@@ -15372,7 +15417,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>SE001000000000EYC2OIN9JYT78UX9PMO4</t>
+          <t>096092</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
@@ -15414,11 +15459,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>42887</v>
+        <v>42879</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15432,42 +15477,42 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t>LUCAS DE MUSSI PALMA</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K142" t="n">
-        <v>107.5</v>
+        <v>213.5</v>
       </c>
       <c r="L142" t="n">
-        <v>118.25</v>
+        <v>234.85</v>
       </c>
       <c r="M142" t="n">
-        <v>10.75</v>
+        <v>21.35</v>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>21:41</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="O142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -15477,7 +15522,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>GQRQAP</t>
+          <t>NM7I3M</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
@@ -15519,11 +15564,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>42890</v>
+        <v>42880</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15541,38 +15586,38 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K143" t="n">
-        <v>242</v>
+        <v>170</v>
       </c>
       <c r="L143" t="n">
-        <v>266.2</v>
+        <v>187</v>
       </c>
       <c r="M143" t="n">
-        <v>24.2</v>
+        <v>17</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="O143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -15582,7 +15627,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>997920</t>
+          <t>37820J</t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
@@ -15624,11 +15669,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>21:58</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>42891</v>
+        <v>42884</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15642,33 +15687,33 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K144" t="n">
-        <v>150</v>
+        <v>168.5</v>
       </c>
       <c r="L144" t="n">
-        <v>165</v>
+        <v>185.35</v>
       </c>
       <c r="M144" t="n">
-        <v>15</v>
+        <v>16.85</v>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="O144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
@@ -15687,7 +15732,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>670309</t>
+          <t>SE001000000000EYC2OIN9JYT78UX9PMO4</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
@@ -15729,11 +15774,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>21:59</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>42892</v>
+        <v>42887</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15747,33 +15792,33 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K145" t="n">
-        <v>136.5</v>
+        <v>107.5</v>
       </c>
       <c r="L145" t="n">
-        <v>150.15</v>
+        <v>118.25</v>
       </c>
       <c r="M145" t="n">
-        <v>13.65</v>
+        <v>10.75</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>21:56</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="O145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
@@ -15792,7 +15837,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>563667</t>
+          <t>GQRQAP</t>
         </is>
       </c>
       <c r="T145" t="inlineStr">
@@ -15834,11 +15879,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>42895</v>
+        <v>42890</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15852,42 +15897,42 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>252</v>
+        <v>18</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K146" t="n">
-        <v>277</v>
+        <v>242</v>
       </c>
       <c r="L146" t="n">
-        <v>304.7</v>
+        <v>266.2</v>
       </c>
       <c r="M146" t="n">
-        <v>27.7</v>
+        <v>24.2</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="O146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -15897,7 +15942,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>SE001000000000DNMWM927LRPRCSQYF6FD</t>
+          <t>997920</t>
         </is>
       </c>
       <c r="T146" t="inlineStr">
@@ -15939,11 +15984,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>42897</v>
+        <v>42891</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15957,29 +16002,29 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>152</v>
+        <v>5</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K147" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="L147" t="n">
-        <v>114.4</v>
+        <v>165</v>
       </c>
       <c r="M147" t="n">
-        <v>10.4</v>
+        <v>15</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="O147" t="n">
@@ -15987,12 +16032,12 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -16002,7 +16047,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>053957</t>
+          <t>670309</t>
         </is>
       </c>
       <c r="T147" t="inlineStr">
@@ -16044,11 +16089,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>22:28</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>42902</v>
+        <v>42892</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16062,11 +16107,11 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -16074,30 +16119,30 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>213</v>
+        <v>136.5</v>
       </c>
       <c r="L148" t="n">
-        <v>234.3</v>
+        <v>150.15</v>
       </c>
       <c r="M148" t="n">
-        <v>21.3</v>
+        <v>13.65</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>22:27</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="O148" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -16107,7 +16152,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>675040</t>
+          <t>563667</t>
         </is>
       </c>
       <c r="T148" t="inlineStr">
@@ -16149,11 +16194,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>42908</v>
+        <v>42895</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16171,38 +16216,38 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K149" t="n">
-        <v>517</v>
+        <v>277</v>
       </c>
       <c r="L149" t="n">
-        <v>568.7</v>
+        <v>304.7</v>
       </c>
       <c r="M149" t="n">
-        <v>51.7</v>
+        <v>27.7</v>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="O149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -16212,7 +16257,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>382074</t>
+          <t>SE001000000000DNMWM927LRPRCSQYF6FD</t>
         </is>
       </c>
       <c r="T149" t="inlineStr">
@@ -16254,11 +16299,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>42921</v>
+        <v>42897</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16272,11 +16317,11 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>18</v>
+        <v>152</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -16284,30 +16329,30 @@
         </is>
       </c>
       <c r="K150" t="n">
-        <v>149.5</v>
+        <v>104</v>
       </c>
       <c r="L150" t="n">
-        <v>164.45</v>
+        <v>114.4</v>
       </c>
       <c r="M150" t="n">
-        <v>14.95</v>
+        <v>10.4</v>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>23:18</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="O150" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -16317,7 +16362,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>761573</t>
+          <t>053957</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
@@ -16349,21 +16394,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>sáb</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>43068</v>
+        <v>42902</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16377,29 +16422,29 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>208</v>
+        <v>29</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K151" t="n">
-        <v>49</v>
+        <v>213</v>
       </c>
       <c r="L151" t="n">
-        <v>53.9</v>
+        <v>234.3</v>
       </c>
       <c r="M151" t="n">
-        <v>4.9</v>
+        <v>21.3</v>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="O151" t="n">
@@ -16407,12 +16452,12 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -16422,7 +16467,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>SE0010000000005BGOKX89TR6Z1P90H0IQ</t>
+          <t>675040</t>
         </is>
       </c>
       <c r="T151" t="inlineStr">
@@ -16454,21 +16499,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>sáb</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>43070</v>
+        <v>42908</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16482,33 +16527,33 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>185</v>
+        <v>244</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K152" t="n">
-        <v>61</v>
+        <v>517</v>
       </c>
       <c r="L152" t="n">
-        <v>67.09999999999999</v>
+        <v>568.7</v>
       </c>
       <c r="M152" t="n">
-        <v>6.1</v>
+        <v>51.7</v>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="O152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P152" t="inlineStr">
         <is>
@@ -16527,7 +16572,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>SE0010000000003TF69RVH78D7TTBQDPYL</t>
+          <t>382074</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
@@ -16559,21 +16604,21 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>sáb</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>43075</v>
+        <v>42921</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16587,42 +16632,42 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K153" t="n">
-        <v>148</v>
+        <v>149.5</v>
       </c>
       <c r="L153" t="n">
-        <v>162.8</v>
+        <v>164.45</v>
       </c>
       <c r="M153" t="n">
-        <v>14.8</v>
+        <v>14.95</v>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:18</t>
         </is>
       </c>
       <c r="O153" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -16632,7 +16677,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>693061</t>
+          <t>761573</t>
         </is>
       </c>
       <c r="T153" t="inlineStr">
@@ -16674,11 +16719,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>43076</v>
+        <v>42983</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16687,38 +16732,38 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>BRUNO DA SILVA INACIO</t>
+          <t>LUCAS DE MUSSI PALMA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>6</v>
+        <v>266</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K154" t="n">
-        <v>226</v>
+        <v>135.5</v>
       </c>
       <c r="L154" t="n">
-        <v>248.6</v>
+        <v>149.05</v>
       </c>
       <c r="M154" t="n">
-        <v>22.6</v>
+        <v>13.55</v>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="O154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P154" t="inlineStr">
         <is>
@@ -16737,7 +16782,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>NKWQWJ</t>
+          <t>SE0010000000003J97Y0CVGVWA1XEXZKUC</t>
         </is>
       </c>
       <c r="T154" t="inlineStr">
@@ -16779,11 +16824,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>43078</v>
+        <v>43013</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16792,16 +16837,16 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>BRUNO DA SILVA INACIO</t>
+          <t>LUCAS DE MUSSI PALMA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -16809,21 +16854,21 @@
         </is>
       </c>
       <c r="K155" t="n">
-        <v>147.5</v>
+        <v>87</v>
       </c>
       <c r="L155" t="n">
-        <v>162.25</v>
+        <v>95.7</v>
       </c>
       <c r="M155" t="n">
-        <v>14.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="O155" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P155" t="inlineStr">
         <is>
@@ -16842,7 +16887,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>SE001000000000J12JYWXHFUAGJV1H95K2</t>
+          <t>SE00100000000000DMP4DVRLHNW7TT7DJ5</t>
         </is>
       </c>
       <c r="T155" t="inlineStr">
@@ -16884,11 +16929,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>43085</v>
+        <v>43068</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16902,11 +16947,11 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3</v>
+        <v>208</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -16914,30 +16959,30 @@
         </is>
       </c>
       <c r="K156" t="n">
-        <v>196.5</v>
+        <v>49</v>
       </c>
       <c r="L156" t="n">
-        <v>216.15</v>
+        <v>53.9</v>
       </c>
       <c r="M156" t="n">
-        <v>19.65</v>
+        <v>4.9</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>23:43</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="O156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -16947,7 +16992,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>SE0010000000002KY0QRJOGY8CQ7RX0KB2</t>
+          <t>SE0010000000005BGOKX89TR6Z1P90H0IQ</t>
         </is>
       </c>
       <c r="T156" t="inlineStr">
@@ -16979,21 +17024,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>dom</t>
+          <t>sáb</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>43117</v>
+        <v>43070</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17007,11 +17052,11 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>7</v>
+        <v>185</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -17019,30 +17064,30 @@
         </is>
       </c>
       <c r="K157" t="n">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="L157" t="n">
-        <v>136.4</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M157" t="n">
-        <v>12.4</v>
+        <v>6.1</v>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="O157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -17052,7 +17097,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>SE001000000000BNF7RTZCV7MJ5B6IWFTE</t>
+          <t>SE0010000000003TF69RVH78D7TTBQDPYL</t>
         </is>
       </c>
       <c r="T157" t="inlineStr">
@@ -17084,21 +17129,21 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>dom</t>
+          <t>sáb</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>22:07</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>43138</v>
+        <v>43075</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17112,42 +17157,42 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K158" t="n">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="L158" t="n">
-        <v>103.4</v>
+        <v>162.8</v>
       </c>
       <c r="M158" t="n">
-        <v>9.4</v>
+        <v>14.8</v>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="O158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -17157,7 +17202,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>071332</t>
+          <t>693061</t>
         </is>
       </c>
       <c r="T158" t="inlineStr">
@@ -17189,21 +17234,21 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>dom</t>
+          <t>sáb</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>43153</v>
+        <v>43076</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17217,33 +17262,33 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>179</v>
+        <v>6</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K159" t="n">
-        <v>144</v>
+        <v>226</v>
       </c>
       <c r="L159" t="n">
-        <v>158.4</v>
+        <v>248.6</v>
       </c>
       <c r="M159" t="n">
-        <v>14.4</v>
+        <v>22.6</v>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>22:23</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="O159" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P159" t="inlineStr">
         <is>
@@ -17262,7 +17307,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>353911</t>
+          <t>NKWQWJ</t>
         </is>
       </c>
       <c r="T159" t="inlineStr">
@@ -17294,21 +17339,21 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>sáb</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>43212</v>
+        <v>43078</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17322,42 +17367,42 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>JOSE HENRIQUE ROSA</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K160" t="n">
-        <v>113</v>
+        <v>147.5</v>
       </c>
       <c r="L160" t="n">
-        <v>124.3</v>
+        <v>162.25</v>
       </c>
       <c r="M160" t="n">
-        <v>11.3</v>
+        <v>14.75</v>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="O160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -17367,7 +17412,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>090576</t>
+          <t>SE001000000000J12JYWXHFUAGJV1H95K2</t>
         </is>
       </c>
       <c r="T160" t="inlineStr">
@@ -17399,21 +17444,21 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>sáb</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>21:16</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>43219</v>
+        <v>43085</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17427,42 +17472,42 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K161" t="n">
-        <v>127</v>
+        <v>196.5</v>
       </c>
       <c r="L161" t="n">
-        <v>139.7</v>
+        <v>216.15</v>
       </c>
       <c r="M161" t="n">
-        <v>12.7</v>
+        <v>19.65</v>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>23:43</t>
         </is>
       </c>
       <c r="O161" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -17472,7 +17517,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>675820</t>
+          <t>SE0010000000002KY0QRJOGY8CQ7RX0KB2</t>
         </is>
       </c>
       <c r="T161" t="inlineStr">
@@ -17504,21 +17549,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>dom</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>43222</v>
+        <v>43117</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17532,11 +17577,11 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>157</v>
+        <v>7</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -17544,17 +17589,17 @@
         </is>
       </c>
       <c r="K162" t="n">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="L162" t="n">
-        <v>55</v>
+        <v>136.4</v>
       </c>
       <c r="M162" t="n">
-        <v>5</v>
+        <v>12.4</v>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="O162" t="n">
@@ -17562,12 +17607,12 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -17577,7 +17622,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>SE001000000000BAAX2ZP5UG8BKVHSXH50</t>
+          <t>SE001000000000BNF7RTZCV7MJ5B6IWFTE</t>
         </is>
       </c>
       <c r="T162" t="inlineStr">
@@ -17609,21 +17654,21 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>qua</t>
+          <t>dom</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>22:26</t>
+          <t>22:07</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>43316</v>
+        <v>43138</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17637,7 +17682,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="I163" t="n">
@@ -17645,34 +17690,34 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K163" t="n">
-        <v>143.5</v>
+        <v>94</v>
       </c>
       <c r="L163" t="n">
-        <v>157.85</v>
+        <v>103.4</v>
       </c>
       <c r="M163" t="n">
-        <v>14.35</v>
+        <v>9.4</v>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>22:26</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="O163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -17682,7 +17727,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>SE001000000000LTU73FWKBD10OF3L03V8</t>
+          <t>071332</t>
         </is>
       </c>
       <c r="T163" t="inlineStr">
@@ -17714,21 +17759,21 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>qua</t>
+          <t>dom</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>43322</v>
+        <v>43153</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17742,33 +17787,33 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>30</v>
+        <v>179</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K164" t="n">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="L164" t="n">
-        <v>102.3</v>
+        <v>158.4</v>
       </c>
       <c r="M164" t="n">
-        <v>9.300000000000001</v>
+        <v>14.4</v>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="O164" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P164" t="inlineStr">
         <is>
@@ -17787,7 +17832,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>SE001000000000NVOTGNE4XR0Y3L26KC27</t>
+          <t>353911</t>
         </is>
       </c>
       <c r="T164" t="inlineStr">
@@ -17819,21 +17864,21 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>43366</v>
+        <v>43212</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17847,33 +17892,33 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t>JOSE HENRIQUE ROSA</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K165" t="n">
-        <v>110.5</v>
+        <v>113</v>
       </c>
       <c r="L165" t="n">
-        <v>121.55</v>
+        <v>124.3</v>
       </c>
       <c r="M165" t="n">
-        <v>11.05</v>
+        <v>11.3</v>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="O165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P165" t="inlineStr">
         <is>
@@ -17892,7 +17937,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>SE001000000000ES3XR8Y7UAQ469LEVJ04</t>
+          <t>090576</t>
         </is>
       </c>
       <c r="T165" t="inlineStr">
@@ -17924,21 +17969,21 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>43370</v>
+        <v>43219</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17956,38 +18001,38 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K166" t="n">
-        <v>124.5</v>
+        <v>127</v>
       </c>
       <c r="L166" t="n">
-        <v>136.95</v>
+        <v>139.7</v>
       </c>
       <c r="M166" t="n">
-        <v>12.45</v>
+        <v>12.7</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="O166" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -17997,7 +18042,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>632855</t>
+          <t>675820</t>
         </is>
       </c>
       <c r="T166" t="inlineStr">
@@ -18029,12 +18074,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -18043,7 +18088,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>43372</v>
+        <v>43222</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18061,38 +18106,38 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>7</v>
+        <v>157</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K167" t="n">
-        <v>159</v>
+        <v>50</v>
       </c>
       <c r="L167" t="n">
-        <v>174.9</v>
+        <v>55</v>
       </c>
       <c r="M167" t="n">
-        <v>15.9</v>
+        <v>5</v>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="O167" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -18102,7 +18147,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>263943</t>
+          <t>SE001000000000BAAX2ZP5UG8BKVHSXH50</t>
         </is>
       </c>
       <c r="T167" t="inlineStr">
@@ -18134,21 +18179,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>qua</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>43379</v>
+        <v>43316</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18162,33 +18207,33 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K168" t="n">
-        <v>191.5</v>
+        <v>143.5</v>
       </c>
       <c r="L168" t="n">
-        <v>210.65</v>
+        <v>157.85</v>
       </c>
       <c r="M168" t="n">
-        <v>19.15</v>
+        <v>14.35</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="O168" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P168" t="inlineStr">
         <is>
@@ -18207,7 +18252,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>546604</t>
+          <t>SE001000000000LTU73FWKBD10OF3L03V8</t>
         </is>
       </c>
       <c r="T168" t="inlineStr">
@@ -18239,21 +18284,21 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>qua</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>43382</v>
+        <v>43322</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18267,33 +18312,33 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K169" t="n">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="L169" t="n">
-        <v>168.3</v>
+        <v>102.3</v>
       </c>
       <c r="M169" t="n">
-        <v>15.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="O169" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P169" t="inlineStr">
         <is>
@@ -18312,7 +18357,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>764107</t>
+          <t>SE001000000000NVOTGNE4XR0Y3L26KC27</t>
         </is>
       </c>
       <c r="T169" t="inlineStr">
@@ -18354,11 +18399,11 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>23:09</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>43416</v>
+        <v>43366</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18372,33 +18417,33 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K170" t="n">
-        <v>208</v>
+        <v>110.5</v>
       </c>
       <c r="L170" t="n">
-        <v>228.8</v>
+        <v>121.55</v>
       </c>
       <c r="M170" t="n">
-        <v>20.8</v>
+        <v>11.05</v>
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="O170" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P170" t="inlineStr">
         <is>
@@ -18417,7 +18462,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>493876</t>
+          <t>SE001000000000ES3XR8Y7UAQ469LEVJ04</t>
         </is>
       </c>
       <c r="T170" t="inlineStr">
@@ -18449,21 +18494,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>43440</v>
+        <v>43370</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18477,33 +18522,33 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K171" t="n">
-        <v>215</v>
+        <v>124.5</v>
       </c>
       <c r="L171" t="n">
-        <v>236.5</v>
+        <v>136.95</v>
       </c>
       <c r="M171" t="n">
-        <v>21.5</v>
+        <v>12.45</v>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="O171" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P171" t="inlineStr">
         <is>
@@ -18522,7 +18567,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>SE001000000000F1E5AHIUVB4LQWT2EN84</t>
+          <t>632855</t>
         </is>
       </c>
       <c r="T171" t="inlineStr">
@@ -18554,21 +18599,21 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>43444</v>
+        <v>43372</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18582,34 +18627,34 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="I172" t="n">
+        <v>7</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Crédito</t>
+        </is>
+      </c>
+      <c r="K172" t="n">
+        <v>159</v>
+      </c>
+      <c r="L172" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="M172" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="O172" t="n">
         <v>6</v>
       </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>PIX</t>
-        </is>
-      </c>
-      <c r="K172" t="n">
-        <v>226</v>
-      </c>
-      <c r="L172" t="n">
-        <v>248.6</v>
-      </c>
-      <c r="M172" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>20:41</t>
-        </is>
-      </c>
-      <c r="O172" t="n">
-        <v>1</v>
-      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>APT88E4F</t>
@@ -18627,7 +18672,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>SE001000000000MXVG7VVGWE51FSSJG811</t>
+          <t>263943</t>
         </is>
       </c>
       <c r="T172" t="inlineStr">
@@ -18659,21 +18704,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>43452</v>
+        <v>43379</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18687,33 +18732,33 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>LUCAS DE MUSSI PALMA</t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>240</v>
+        <v>28</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K173" t="n">
-        <v>257</v>
+        <v>191.5</v>
       </c>
       <c r="L173" t="n">
-        <v>282.7</v>
+        <v>210.65</v>
       </c>
       <c r="M173" t="n">
-        <v>25.7</v>
+        <v>19.15</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="O173" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P173" t="inlineStr">
         <is>
@@ -18732,7 +18777,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>SE0010000000003ISIZLQVHWNRB5HNZ93D</t>
+          <t>546604</t>
         </is>
       </c>
       <c r="T173" t="inlineStr">
@@ -18764,21 +18809,21 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>21:16</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>43454</v>
+        <v>43382</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18792,42 +18837,42 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K174" t="n">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="L174" t="n">
-        <v>57.2</v>
+        <v>168.3</v>
       </c>
       <c r="M174" t="n">
-        <v>5.2</v>
+        <v>15.3</v>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>21:16</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="O174" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -18837,7 +18882,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>SE00100000000043JJOUHKK5TFTY520N79</t>
+          <t>764107</t>
         </is>
       </c>
       <c r="T174" t="inlineStr">
@@ -18869,21 +18914,21 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>23:09</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>43456</v>
+        <v>43416</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18897,33 +18942,33 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>206</v>
+        <v>7</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K175" t="n">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="L175" t="n">
-        <v>281.6</v>
+        <v>228.8</v>
       </c>
       <c r="M175" t="n">
-        <v>25.6</v>
+        <v>20.8</v>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="O175" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P175" t="inlineStr">
         <is>
@@ -18942,7 +18987,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>SE001000000000GESRXQIFWGIFAKZ7ZHDS</t>
+          <t>493876</t>
         </is>
       </c>
       <c r="T175" t="inlineStr">
@@ -18984,11 +19029,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>43458</v>
+        <v>43440</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19002,33 +19047,33 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K176" t="n">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="L176" t="n">
-        <v>249.7</v>
+        <v>236.5</v>
       </c>
       <c r="M176" t="n">
-        <v>22.7</v>
+        <v>21.5</v>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="O176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P176" t="inlineStr">
         <is>
@@ -19047,7 +19092,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>513443</t>
+          <t>SE001000000000F1E5AHIUVB4LQWT2EN84</t>
         </is>
       </c>
       <c r="T176" t="inlineStr">
@@ -19089,11 +19134,11 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>43457</v>
+        <v>43444</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19111,29 +19156,29 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K177" t="n">
-        <v>282</v>
+        <v>226</v>
       </c>
       <c r="L177" t="n">
-        <v>310.2</v>
+        <v>248.6</v>
       </c>
       <c r="M177" t="n">
-        <v>28.2</v>
+        <v>22.6</v>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="O177" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P177" t="inlineStr">
         <is>
@@ -19152,7 +19197,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>956679</t>
+          <t>SE001000000000MXVG7VVGWE51FSSJG811</t>
         </is>
       </c>
       <c r="T177" t="inlineStr">
@@ -19194,11 +19239,11 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>43463</v>
+        <v>43452</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19212,11 +19257,11 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>LUCAS DE MUSSI PALMA</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>155</v>
+        <v>240</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -19224,17 +19269,17 @@
         </is>
       </c>
       <c r="K178" t="n">
-        <v>103</v>
+        <v>257</v>
       </c>
       <c r="L178" t="n">
-        <v>113.3</v>
+        <v>282.7</v>
       </c>
       <c r="M178" t="n">
-        <v>10.3</v>
+        <v>25.7</v>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="O178" t="n">
@@ -19242,12 +19287,12 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -19257,7 +19302,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>SE001000000000NZ8AH9PMU6U4GUOVUG99</t>
+          <t>SE0010000000003ISIZLQVHWNRB5HNZ93D</t>
         </is>
       </c>
       <c r="T178" t="inlineStr">
@@ -19299,11 +19344,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>43470</v>
+        <v>43454</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19317,11 +19362,11 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>260</v>
+        <v>124</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -19329,17 +19374,17 @@
         </is>
       </c>
       <c r="K179" t="n">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="L179" t="n">
-        <v>113.3</v>
+        <v>57.2</v>
       </c>
       <c r="M179" t="n">
-        <v>10.3</v>
+        <v>5.2</v>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="O179" t="n">
@@ -19362,7 +19407,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>SE001000000000LRNKOXW62WFJ77QMEKZY</t>
+          <t>SE00100000000043JJOUHKK5TFTY520N79</t>
         </is>
       </c>
       <c r="T179" t="inlineStr">
@@ -19404,11 +19449,11 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>21:59</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>43480</v>
+        <v>43456</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19422,11 +19467,11 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -19434,21 +19479,21 @@
         </is>
       </c>
       <c r="K180" t="n">
-        <v>54</v>
+        <v>256</v>
       </c>
       <c r="L180" t="n">
-        <v>59.4</v>
+        <v>281.6</v>
       </c>
       <c r="M180" t="n">
-        <v>5.4</v>
+        <v>25.6</v>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>21:59</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="O180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P180" t="inlineStr">
         <is>
@@ -19467,7 +19512,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>SE001000000000CJ48EIJX1TQFVJBXXSV4</t>
+          <t>SE001000000000GESRXQIFWGIFAKZ7ZHDS</t>
         </is>
       </c>
       <c r="T180" t="inlineStr">
@@ -19509,11 +19554,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>43489</v>
+        <v>43458</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19527,33 +19572,33 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K181" t="n">
-        <v>170</v>
+        <v>227</v>
       </c>
       <c r="L181" t="n">
-        <v>187</v>
+        <v>249.7</v>
       </c>
       <c r="M181" t="n">
-        <v>17</v>
+        <v>22.7</v>
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="O181" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P181" t="inlineStr">
         <is>
@@ -19572,7 +19617,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>SE001000000000IG30ONROX5PIXB050M48</t>
+          <t>513443</t>
         </is>
       </c>
       <c r="T181" t="inlineStr">
@@ -19614,11 +19659,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>43502</v>
+        <v>43457</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19632,42 +19677,42 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I182" t="n">
+        <v>7</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Crédito</t>
+        </is>
+      </c>
+      <c r="K182" t="n">
+        <v>282</v>
+      </c>
+      <c r="L182" t="n">
+        <v>310.2</v>
+      </c>
+      <c r="M182" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="O182" t="n">
         <v>5</v>
       </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>Crédito</t>
-        </is>
-      </c>
-      <c r="K182" t="n">
-        <v>136</v>
-      </c>
-      <c r="L182" t="n">
-        <v>149.6</v>
-      </c>
-      <c r="M182" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>22:21</t>
-        </is>
-      </c>
-      <c r="O182" t="n">
-        <v>12</v>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -19677,7 +19722,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>160693</t>
+          <t>956679</t>
         </is>
       </c>
       <c r="T182" t="inlineStr">
@@ -19719,11 +19764,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>43501</v>
+        <v>43463</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19737,42 +19782,42 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>28</v>
+        <v>155</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K183" t="n">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="L183" t="n">
-        <v>187</v>
+        <v>113.3</v>
       </c>
       <c r="M183" t="n">
-        <v>17</v>
+        <v>10.3</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>22:19</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="O183" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -19782,7 +19827,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>Z4XIlk</t>
+          <t>SE001000000000NZ8AH9PMU6U4GUOVUG99</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
@@ -19824,11 +19869,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>43506</v>
+        <v>43470</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19842,11 +19887,11 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -19854,30 +19899,30 @@
         </is>
       </c>
       <c r="K184" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="L184" t="n">
-        <v>126.5</v>
+        <v>113.3</v>
       </c>
       <c r="M184" t="n">
-        <v>11.5</v>
+        <v>10.3</v>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>22:48</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="O184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -19887,7 +19932,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>SE001000000000NBQ8688JJKGB0KNE32D9</t>
+          <t>SE001000000000LRNKOXW62WFJ77QMEKZY</t>
         </is>
       </c>
       <c r="T184" t="inlineStr">
@@ -19929,11 +19974,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>43507</v>
+        <v>43480</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19947,33 +19992,33 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K185" t="n">
-        <v>307</v>
+        <v>54</v>
       </c>
       <c r="L185" t="n">
-        <v>337.7</v>
+        <v>59.4</v>
       </c>
       <c r="M185" t="n">
-        <v>30.7</v>
+        <v>5.4</v>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>22:24</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="O185" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P185" t="inlineStr">
         <is>
@@ -19992,7 +20037,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>091074</t>
+          <t>SE001000000000CJ48EIJX1TQFVJBXXSV4</t>
         </is>
       </c>
       <c r="T185" t="inlineStr">
@@ -20024,21 +20069,21 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>sáb</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>43593</v>
+        <v>43489</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20052,42 +20097,42 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K186" t="n">
-        <v>178.5</v>
+        <v>170</v>
       </c>
       <c r="L186" t="n">
-        <v>196.35</v>
+        <v>187</v>
       </c>
       <c r="M186" t="n">
-        <v>17.85</v>
+        <v>17</v>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="O186" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -20097,7 +20142,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>698660</t>
+          <t>SE001000000000IG30ONROX5PIXB050M48</t>
         </is>
       </c>
       <c r="T186" t="inlineStr">
@@ -20129,21 +20174,21 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>sáb</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>43596</v>
+        <v>43502</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20157,11 +20202,11 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -20169,21 +20214,21 @@
         </is>
       </c>
       <c r="K187" t="n">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="L187" t="n">
-        <v>191.4</v>
+        <v>149.6</v>
       </c>
       <c r="M187" t="n">
-        <v>17.4</v>
+        <v>13.6</v>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>22:21</t>
         </is>
       </c>
       <c r="O187" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P187" t="inlineStr">
         <is>
@@ -20202,7 +20247,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>663065</t>
+          <t>160693</t>
         </is>
       </c>
       <c r="T187" t="inlineStr">
@@ -20234,21 +20279,21 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>sáb</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>43604</v>
+        <v>43501</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20262,33 +20307,33 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
         </is>
       </c>
       <c r="I188" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K188" t="n">
-        <v>133.5</v>
+        <v>170</v>
       </c>
       <c r="L188" t="n">
-        <v>146.85</v>
+        <v>187</v>
       </c>
       <c r="M188" t="n">
-        <v>13.35</v>
+        <v>17</v>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="O188" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="P188" t="inlineStr">
         <is>
@@ -20307,7 +20352,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>SE001000000000NE499ROHU6QPYAH55Z45</t>
+          <t>Z4XIlk</t>
         </is>
       </c>
       <c r="T188" t="inlineStr">
@@ -20339,21 +20384,21 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>sáb</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>43639</v>
+        <v>43506</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20367,11 +20412,11 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>LUCAS DE MUSSI PALMA</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>231</v>
+        <v>1</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -20379,17 +20424,17 @@
         </is>
       </c>
       <c r="K189" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="L189" t="n">
-        <v>117.7</v>
+        <v>126.5</v>
       </c>
       <c r="M189" t="n">
-        <v>10.7</v>
+        <v>11.5</v>
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>21:59</t>
+          <t>22:48</t>
         </is>
       </c>
       <c r="O189" t="n">
@@ -20397,12 +20442,12 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -20412,7 +20457,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>SE001000000000NL4CQAKUYWZWXAJZYT37</t>
+          <t>SE001000000000NBQ8688JJKGB0KNE32D9</t>
         </is>
       </c>
       <c r="T189" t="inlineStr">
@@ -20444,21 +20489,21 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>sáb</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>43643</v>
+        <v>43507</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20472,33 +20517,33 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K190" t="n">
-        <v>73</v>
+        <v>307</v>
       </c>
       <c r="L190" t="n">
-        <v>80.3</v>
+        <v>337.7</v>
       </c>
       <c r="M190" t="n">
-        <v>7.3</v>
+        <v>30.7</v>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:24</t>
         </is>
       </c>
       <c r="O190" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="P190" t="inlineStr">
         <is>
@@ -20517,7 +20562,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>SE001000000000LFZRJEYM9EMTS1CXAUQK</t>
+          <t>091074</t>
         </is>
       </c>
       <c r="T190" t="inlineStr">
@@ -20559,11 +20604,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>43655</v>
+        <v>43593</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20577,29 +20622,29 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>LUCAS DE MUSSI PALMA</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K191" t="n">
-        <v>203.5</v>
+        <v>178.5</v>
       </c>
       <c r="L191" t="n">
-        <v>223.85</v>
+        <v>196.35</v>
       </c>
       <c r="M191" t="n">
-        <v>20.35</v>
+        <v>17.85</v>
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="O191" t="n">
@@ -20607,12 +20652,12 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
@@ -20622,7 +20667,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>SE001000000000CPB2GNUXCUNA38G6P9I7</t>
+          <t>698660</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
@@ -20664,11 +20709,11 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>22:21</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>43659</v>
+        <v>43596</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20682,33 +20727,33 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K192" t="n">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="L192" t="n">
-        <v>210.1</v>
+        <v>191.4</v>
       </c>
       <c r="M192" t="n">
-        <v>19.1</v>
+        <v>17.4</v>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="O192" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="P192" t="inlineStr">
         <is>
@@ -20727,7 +20772,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>157228</t>
+          <t>663065</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
@@ -20769,11 +20814,11 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>22:23</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>43662</v>
+        <v>43604</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20791,29 +20836,29 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>179</v>
+        <v>12</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K193" t="n">
-        <v>173</v>
+        <v>133.5</v>
       </c>
       <c r="L193" t="n">
-        <v>190.3</v>
+        <v>146.85</v>
       </c>
       <c r="M193" t="n">
-        <v>17.3</v>
+        <v>13.35</v>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="O193" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="P193" t="inlineStr">
         <is>
@@ -20832,7 +20877,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>834435</t>
+          <t>SE001000000000NE499ROHU6QPYAH55Z45</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
@@ -20874,11 +20919,11 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>22:26</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>43666</v>
+        <v>43639</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20892,25 +20937,25 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>LUCAS DE MUSSI PALMA</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>12</v>
+        <v>231</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K194" t="n">
-        <v>177.5</v>
+        <v>107</v>
       </c>
       <c r="L194" t="n">
-        <v>195.25</v>
+        <v>117.7</v>
       </c>
       <c r="M194" t="n">
-        <v>17.75</v>
+        <v>10.7</v>
       </c>
       <c r="N194" t="inlineStr">
         <is>
@@ -20918,16 +20963,16 @@
         </is>
       </c>
       <c r="O194" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
@@ -20937,7 +20982,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>408181</t>
+          <t>SE001000000000NL4CQAKUYWZWXAJZYT37</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
@@ -20979,11 +21024,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>43669</v>
+        <v>43643</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20997,29 +21042,29 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>LUCAS DE MUSSI PALMA</t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K195" t="n">
-        <v>170.5</v>
+        <v>73</v>
       </c>
       <c r="L195" t="n">
-        <v>187.55</v>
+        <v>80.3</v>
       </c>
       <c r="M195" t="n">
-        <v>17.05</v>
+        <v>7.3</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="O195" t="n">
@@ -21027,12 +21072,12 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
@@ -21042,7 +21087,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>025713</t>
+          <t>SE001000000000LFZRJEYM9EMTS1CXAUQK</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
@@ -21084,11 +21129,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>43672</v>
+        <v>43655</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21106,7 +21151,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -21114,30 +21159,30 @@
         </is>
       </c>
       <c r="K196" t="n">
-        <v>164</v>
+        <v>203.5</v>
       </c>
       <c r="L196" t="n">
-        <v>180.4</v>
+        <v>223.85</v>
       </c>
       <c r="M196" t="n">
-        <v>16.4</v>
+        <v>20.35</v>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="O196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
@@ -21147,7 +21192,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>SE001000000000K5HDRBZCRIF6U919KTH0</t>
+          <t>SE001000000000CPB2GNUXCUNA38G6P9I7</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
@@ -21179,21 +21224,21 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>sáb</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>22:21</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>43863</v>
+        <v>43659</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21207,33 +21252,33 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K197" t="n">
-        <v>95</v>
+        <v>191</v>
       </c>
       <c r="L197" t="n">
-        <v>104.5</v>
+        <v>210.1</v>
       </c>
       <c r="M197" t="n">
-        <v>9.5</v>
+        <v>19.1</v>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="O197" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="P197" t="inlineStr">
         <is>
@@ -21252,7 +21297,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>818764</t>
+          <t>157228</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
@@ -21284,21 +21329,21 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>sáb</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>43865</v>
+        <v>43662</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21312,33 +21357,33 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>31</v>
+        <v>179</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K198" t="n">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="L198" t="n">
-        <v>121</v>
+        <v>190.3</v>
       </c>
       <c r="M198" t="n">
-        <v>11</v>
+        <v>17.3</v>
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="O198" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="P198" t="inlineStr">
         <is>
@@ -21357,7 +21402,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>185246</t>
+          <t>834435</t>
         </is>
       </c>
       <c r="T198" t="inlineStr">
@@ -21389,21 +21434,21 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>sáb</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>21:58</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>43898</v>
+        <v>43666</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21417,7 +21462,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="I199" t="n">
@@ -21429,21 +21474,21 @@
         </is>
       </c>
       <c r="K199" t="n">
-        <v>271</v>
+        <v>177.5</v>
       </c>
       <c r="L199" t="n">
-        <v>298.1</v>
+        <v>195.25</v>
       </c>
       <c r="M199" t="n">
-        <v>27.1</v>
+        <v>17.75</v>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="O199" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="P199" t="inlineStr">
         <is>
@@ -21462,7 +21507,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>069594</t>
+          <t>408181</t>
         </is>
       </c>
       <c r="T199" t="inlineStr">
@@ -21494,21 +21539,21 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>sáb</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>43919</v>
+        <v>43669</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21522,33 +21567,33 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t>LUCAS DE MUSSI PALMA</t>
         </is>
       </c>
       <c r="I200" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K200" t="n">
-        <v>316.5</v>
+        <v>170.5</v>
       </c>
       <c r="L200" t="n">
-        <v>348.15</v>
+        <v>187.55</v>
       </c>
       <c r="M200" t="n">
-        <v>31.65</v>
+        <v>17.05</v>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="O200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P200" t="inlineStr">
         <is>
@@ -21567,7 +21612,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>SE001000000000KWIPD52AO3VWFGO1E4TC</t>
+          <t>025713</t>
         </is>
       </c>
       <c r="T200" t="inlineStr">
@@ -21599,21 +21644,21 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>sáb</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>43933</v>
+        <v>43672</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21627,33 +21672,33 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>LUCAS DE MUSSI PALMA</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K201" t="n">
-        <v>349.5</v>
+        <v>164</v>
       </c>
       <c r="L201" t="n">
-        <v>384.45</v>
+        <v>180.4</v>
       </c>
       <c r="M201" t="n">
-        <v>34.95</v>
+        <v>16.4</v>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="O201" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P201" t="inlineStr">
         <is>
@@ -21672,7 +21717,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>097612</t>
+          <t>SE001000000000K5HDRBZCRIF6U919KTH0</t>
         </is>
       </c>
       <c r="T201" t="inlineStr">
@@ -21704,21 +21749,21 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>qua</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>43992</v>
+        <v>43863</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21732,33 +21777,33 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K202" t="n">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="L202" t="n">
-        <v>209</v>
+        <v>104.5</v>
       </c>
       <c r="M202" t="n">
-        <v>19</v>
+        <v>9.5</v>
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="O202" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P202" t="inlineStr">
         <is>
@@ -21777,7 +21822,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>SZEOPK</t>
+          <t>818764</t>
         </is>
       </c>
       <c r="T202" t="inlineStr">
@@ -21809,21 +21854,21 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>44045</v>
+        <v>43865</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21841,7 +21886,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -21849,21 +21894,21 @@
         </is>
       </c>
       <c r="K203" t="n">
-        <v>166.5</v>
+        <v>110</v>
       </c>
       <c r="L203" t="n">
-        <v>183.15</v>
+        <v>121</v>
       </c>
       <c r="M203" t="n">
-        <v>16.65</v>
+        <v>11</v>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="O203" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="P203" t="inlineStr">
         <is>
@@ -21882,7 +21927,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>YGdfWb</t>
+          <t>185246</t>
         </is>
       </c>
       <c r="T203" t="inlineStr">
@@ -21914,21 +21959,21 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>44050</v>
+        <v>43898</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21946,7 +21991,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -21954,30 +21999,30 @@
         </is>
       </c>
       <c r="K204" t="n">
-        <v>342</v>
+        <v>271</v>
       </c>
       <c r="L204" t="n">
-        <v>376.2</v>
+        <v>298.1</v>
       </c>
       <c r="M204" t="n">
-        <v>34.2</v>
+        <v>27.1</v>
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="O204" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
@@ -21987,7 +22032,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>655614</t>
+          <t>069594</t>
         </is>
       </c>
       <c r="T204" t="inlineStr">
@@ -22019,21 +22064,21 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>44053</v>
+        <v>43919</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22047,42 +22092,42 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I205" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K205" t="n">
-        <v>256</v>
+        <v>316.5</v>
       </c>
       <c r="L205" t="n">
-        <v>281.6</v>
+        <v>348.15</v>
       </c>
       <c r="M205" t="n">
-        <v>25.6</v>
+        <v>31.65</v>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="O205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
@@ -22092,7 +22137,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>131765</t>
+          <t>SE001000000000KWIPD52AO3VWFGO1E4TC</t>
         </is>
       </c>
       <c r="T205" t="inlineStr">
@@ -22124,21 +22169,21 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>44062</v>
+        <v>43933</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22156,38 +22201,38 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K206" t="n">
-        <v>103</v>
+        <v>349.5</v>
       </c>
       <c r="L206" t="n">
-        <v>113.3</v>
+        <v>384.45</v>
       </c>
       <c r="M206" t="n">
-        <v>10.3</v>
+        <v>34.95</v>
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="O206" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
@@ -22197,7 +22242,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>SE00100000000030GP34S13B3CVBJ2XH7D</t>
+          <t>097612</t>
         </is>
       </c>
       <c r="T206" t="inlineStr">
@@ -22229,21 +22274,21 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>qua</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>44066</v>
+        <v>43992</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22257,42 +22302,42 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="I207" t="n">
-        <v>244</v>
+        <v>7</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K207" t="n">
-        <v>272</v>
+        <v>190</v>
       </c>
       <c r="L207" t="n">
-        <v>299.2</v>
+        <v>209</v>
       </c>
       <c r="M207" t="n">
-        <v>27.2</v>
+        <v>19</v>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="O207" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
@@ -22302,7 +22347,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>SE001000000000AN89T5HZ1RSPG5V5B2XE</t>
+          <t>SZEOPK</t>
         </is>
       </c>
       <c r="T207" t="inlineStr">
@@ -22344,11 +22389,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>44081</v>
+        <v>44045</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22366,38 +22411,38 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K208" t="n">
-        <v>114.5</v>
+        <v>166.5</v>
       </c>
       <c r="L208" t="n">
-        <v>125.95</v>
+        <v>183.15</v>
       </c>
       <c r="M208" t="n">
-        <v>11.45</v>
+        <v>16.65</v>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="O208" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>PDV 02 em 108 de 108 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
@@ -22407,7 +22452,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>MVSSSI</t>
+          <t>YGdfWb</t>
         </is>
       </c>
       <c r="T208" t="inlineStr">
@@ -22439,21 +22484,21 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>44136</v>
+        <v>44050</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22467,11 +22512,11 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I209" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -22479,30 +22524,30 @@
         </is>
       </c>
       <c r="K209" t="n">
-        <v>168</v>
+        <v>342</v>
       </c>
       <c r="L209" t="n">
-        <v>184.8</v>
+        <v>376.2</v>
       </c>
       <c r="M209" t="n">
-        <v>16.8</v>
+        <v>34.2</v>
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="O209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
@@ -22512,7 +22557,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>139742</t>
+          <t>655614</t>
         </is>
       </c>
       <c r="T209" t="inlineStr">
@@ -22544,21 +22589,21 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>44138</v>
+        <v>44053</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22572,29 +22617,29 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K210" t="n">
-        <v>227.5</v>
+        <v>256</v>
       </c>
       <c r="L210" t="n">
-        <v>250.25</v>
+        <v>281.6</v>
       </c>
       <c r="M210" t="n">
-        <v>22.75</v>
+        <v>25.6</v>
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="O210" t="n">
@@ -22602,12 +22647,12 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
@@ -22617,7 +22662,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>vznBrB</t>
+          <t>131765</t>
         </is>
       </c>
       <c r="T210" t="inlineStr">
@@ -22649,21 +22694,21 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>44157</v>
+        <v>44062</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22677,42 +22722,42 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K211" t="n">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="L211" t="n">
-        <v>151.8</v>
+        <v>113.3</v>
       </c>
       <c r="M211" t="n">
-        <v>13.8</v>
+        <v>10.3</v>
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="O211" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
@@ -22722,7 +22767,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>080164</t>
+          <t>SE00100000000030GP34S13B3CVBJ2XH7D</t>
         </is>
       </c>
       <c r="T211" t="inlineStr">
@@ -22754,21 +22799,21 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>44163</v>
+        <v>44066</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22782,42 +22827,42 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="I212" t="n">
-        <v>15</v>
+        <v>244</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K212" t="n">
-        <v>158.5</v>
+        <v>272</v>
       </c>
       <c r="L212" t="n">
-        <v>174.35</v>
+        <v>299.2</v>
       </c>
       <c r="M212" t="n">
-        <v>15.85</v>
+        <v>27.2</v>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>21:37</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="O212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
@@ -22827,7 +22872,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>685816</t>
+          <t>SE001000000000AN89T5HZ1RSPG5V5B2XE</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
@@ -22859,21 +22904,21 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>44170</v>
+        <v>44081</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22887,11 +22932,11 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I213" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -22899,30 +22944,30 @@
         </is>
       </c>
       <c r="K213" t="n">
-        <v>212.5</v>
+        <v>114.5</v>
       </c>
       <c r="L213" t="n">
-        <v>233.75</v>
+        <v>125.95</v>
       </c>
       <c r="M213" t="n">
-        <v>21.25</v>
+        <v>11.45</v>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>21:41</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="O213" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
@@ -22932,7 +22977,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>415759</t>
+          <t>MVSSSI</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
@@ -22974,11 +23019,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>44220</v>
+        <v>44136</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22992,33 +23037,33 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="I214" t="n">
-        <v>227</v>
+        <v>30</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K214" t="n">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="L214" t="n">
-        <v>128.7</v>
+        <v>184.8</v>
       </c>
       <c r="M214" t="n">
-        <v>11.7</v>
+        <v>16.8</v>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="O214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P214" t="inlineStr">
         <is>
@@ -23037,7 +23082,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>SE001000000000J14Q1TG3DZUVC81ORKC1</t>
+          <t>139742</t>
         </is>
       </c>
       <c r="T214" t="inlineStr">
@@ -23069,21 +23114,21 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>44555</v>
+        <v>44138</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23097,33 +23142,33 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="I215" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K215" t="n">
-        <v>220</v>
+        <v>227.5</v>
       </c>
       <c r="L215" t="n">
-        <v>242</v>
+        <v>250.25</v>
       </c>
       <c r="M215" t="n">
-        <v>22</v>
+        <v>22.75</v>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="O215" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="P215" t="inlineStr">
         <is>
@@ -23142,7 +23187,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>SE001000000000J26ZYARRMKJWH476N892</t>
+          <t>vznBrB</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
@@ -23174,21 +23219,21 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>44559</v>
+        <v>44157</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23202,33 +23247,33 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="K216" t="n">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="L216" t="n">
-        <v>176</v>
+        <v>151.8</v>
       </c>
       <c r="M216" t="n">
-        <v>16</v>
+        <v>13.8</v>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="O216" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P216" t="inlineStr">
         <is>
@@ -23247,7 +23292,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>SE001000000000KWTAY4C457ZT2V9UCL55</t>
+          <t>080164</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
@@ -23279,61 +23324,61 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>44163</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>002 - IS01 - PDV 02</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>15</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Crédito</t>
+        </is>
+      </c>
+      <c r="K217" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="L217" t="n">
+        <v>174.35</v>
+      </c>
+      <c r="M217" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
           <t>21:37</t>
         </is>
       </c>
-      <c r="E217" t="n">
-        <v>44561</v>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>002 - IS01 - PDV 02</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>BRUNO DA SILVA INACIO</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
-        </is>
-      </c>
-      <c r="I217" t="n">
-        <v>29</v>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>Crédito</t>
-        </is>
-      </c>
-      <c r="K217" t="n">
-        <v>144</v>
-      </c>
-      <c r="L217" t="n">
-        <v>158.4</v>
-      </c>
-      <c r="M217" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="N217" t="inlineStr">
-        <is>
-          <t>21:28</t>
-        </is>
-      </c>
       <c r="O217" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P217" t="inlineStr">
         <is>
@@ -23352,7 +23397,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>681885</t>
+          <t>685816</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
@@ -23384,21 +23429,21 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>44571</v>
+        <v>44170</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23412,33 +23457,33 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="I218" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="K218" t="n">
-        <v>255</v>
+        <v>212.5</v>
       </c>
       <c r="L218" t="n">
-        <v>280.5</v>
+        <v>233.75</v>
       </c>
       <c r="M218" t="n">
-        <v>25.5</v>
+        <v>21.25</v>
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="O218" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="P218" t="inlineStr">
         <is>
@@ -23457,7 +23502,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>263017</t>
+          <t>415759</t>
         </is>
       </c>
       <c r="T218" t="inlineStr">
@@ -23489,21 +23534,21 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>44573</v>
+        <v>44220</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23517,33 +23562,33 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="I219" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K219" t="n">
-        <v>145.5</v>
+        <v>117</v>
       </c>
       <c r="L219" t="n">
-        <v>160.05</v>
+        <v>128.7</v>
       </c>
       <c r="M219" t="n">
-        <v>14.55</v>
+        <v>11.7</v>
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="O219" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P219" t="inlineStr">
         <is>
@@ -23562,7 +23607,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>348947</t>
+          <t>SE001000000000J14Q1TG3DZUVC81ORKC1</t>
         </is>
       </c>
       <c r="T219" t="inlineStr">
@@ -23604,88 +23649,613 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>44555</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>002 - IS01 - PDV 02</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>30</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>PIX</t>
+        </is>
+      </c>
+      <c r="K220" t="n">
+        <v>220</v>
+      </c>
+      <c r="L220" t="n">
+        <v>242</v>
+      </c>
+      <c r="M220" t="n">
+        <v>22</v>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="O220" t="n">
+        <v>17</v>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>APT88F78</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>SE001000000000J26ZYARRMKJWH476N892</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>nenhum</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>nenhuma</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>fechada</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>outubro/2026 (01 a 20)</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>44559</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>002 - IS01 - PDV 02</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>3</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>PIX</t>
+        </is>
+      </c>
+      <c r="K221" t="n">
+        <v>160</v>
+      </c>
+      <c r="L221" t="n">
+        <v>176</v>
+      </c>
+      <c r="M221" t="n">
+        <v>16</v>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="O221" t="n">
+        <v>1</v>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>APT88F78</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>SE001000000000KWTAY4C457ZT2V9UCL55</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>nenhum</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>nenhuma</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>fechada</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>outubro/2026 (01 a 20)</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>21:37</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>44561</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>002 - IS01 - PDV 02</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>29</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Crédito</t>
+        </is>
+      </c>
+      <c r="K222" t="n">
+        <v>144</v>
+      </c>
+      <c r="L222" t="n">
+        <v>158.4</v>
+      </c>
+      <c r="M222" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>21:28</t>
+        </is>
+      </c>
+      <c r="O222" t="n">
+        <v>8</v>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>APT88F78</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>681885</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>nenhum</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>nenhuma</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>fechada</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>outubro/2026 (01 a 20)</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>44571</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>002 - IS01 - PDV 02</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>26</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="K223" t="n">
+        <v>255</v>
+      </c>
+      <c r="L223" t="n">
+        <v>280.5</v>
+      </c>
+      <c r="M223" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="O223" t="n">
+        <v>19</v>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>APT88F78</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>263017</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>nenhum</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>nenhuma</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>fechada</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>outubro/2026 (01 a 20)</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>44573</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>002 - IS01 - PDV 02</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>214</v>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="K224" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="L224" t="n">
+        <v>160.05</v>
+      </c>
+      <c r="M224" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="O224" t="n">
+        <v>3</v>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>APT88F78</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>348947</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>nenhum</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>nenhuma</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>fechada</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>outubro/2026 (01 a 20)</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
           <t>22:51</t>
         </is>
       </c>
-      <c r="E220" t="n">
+      <c r="E225" t="n">
         <v>44584</v>
       </c>
-      <c r="F220" t="inlineStr">
+      <c r="F225" t="inlineStr">
         <is>
           <t>002 - IS01 - PDV 02</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
+      <c r="G225" t="inlineStr">
         <is>
           <t>BRUNO DA SILVA INACIO</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
+      <c r="H225" t="inlineStr">
         <is>
           <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
-      <c r="I220" t="n">
+      <c r="I225" t="n">
         <v>8</v>
       </c>
-      <c r="J220" t="inlineStr">
+      <c r="J225" t="inlineStr">
         <is>
           <t>Débito</t>
         </is>
       </c>
-      <c r="K220" t="n">
+      <c r="K225" t="n">
         <v>257</v>
       </c>
-      <c r="L220" t="n">
+      <c r="L225" t="n">
         <v>282.7</v>
       </c>
-      <c r="M220" t="n">
+      <c r="M225" t="n">
         <v>25.7</v>
       </c>
-      <c r="N220" t="inlineStr">
+      <c r="N225" t="inlineStr">
         <is>
           <t>22:44</t>
         </is>
       </c>
-      <c r="O220" t="n">
+      <c r="O225" t="n">
         <v>7</v>
       </c>
-      <c r="P220" t="inlineStr">
+      <c r="P225" t="inlineStr">
         <is>
           <t>APT88F78</t>
         </is>
       </c>
-      <c r="Q220" t="inlineStr">
+      <c r="Q225" t="inlineStr">
         <is>
           <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
-      <c r="R220" t="inlineStr">
+      <c r="R225" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="S220" t="inlineStr">
+      <c r="S225" t="inlineStr">
         <is>
           <t>FDU3XH</t>
         </is>
       </c>
-      <c r="T220" t="inlineStr">
+      <c r="T225" t="inlineStr">
         <is>
           <t>nenhum</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="U225" t="inlineStr">
         <is>
           <t>nenhuma</t>
         </is>
       </c>
-      <c r="V220" t="inlineStr">
+      <c r="V225" t="inlineStr">
         <is>
           <t>não</t>
         </is>
       </c>
-      <c r="W220" t="inlineStr">
+      <c r="W225" t="inlineStr">
         <is>
           <t>fechada</t>
         </is>
